--- a/docs/Strong decision table.xlsx
+++ b/docs/Strong decision table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bible_study_projects\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55E6DCE2-70BA-40F8-B5A7-8E658C4C11A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE0E5CB-7FD6-423A-BB25-4C77E27EACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{39AA27BD-B3D9-4F94-BF76-F557A658E6B8}"/>
   </bookViews>
@@ -179,10 +179,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,10 +524,10 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="75.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="76" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -548,7 +551,7 @@
       <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -562,7 +565,7 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -576,7 +579,7 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -590,7 +593,7 @@
       <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -604,7 +607,7 @@
       <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -618,7 +621,7 @@
       <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -632,7 +635,7 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -646,11 +649,11 @@
       <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -660,11 +663,11 @@
       <c r="C11" t="s">
         <v>4</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -674,7 +677,7 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
